--- a/posts/2026-04-26_asturias-mancha-quesera/AOC-Mancha_quesera_europa_update-claude-202604.xlsx
+++ b/posts/2026-04-26_asturias-mancha-quesera/AOC-Mancha_quesera_europa_update-claude-202604.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/blog-trabajo/asturias-mancha-quesera/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanr\GitHub\blog\posts\2026-04-26_asturias-mancha-quesera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{A835B32E-AF8A-43C3-A7DE-085E6D9B2406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{603DDBE3-EF76-45CF-85D3-22C2BA41E371}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1FD8A8-9953-4FFB-BAAD-C0E12AA059BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5190" yWindow="3135" windowWidth="17820" windowHeight="11190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prod por pais" sheetId="1" r:id="rId1"/>
@@ -2697,7 +2697,7 @@
       <name val="Inherit"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2794,8 +2794,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -2980,11 +2986,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDFE2E5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDFE2E5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDFE2E5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDFE2E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3222,19 +3243,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3431,10 +3458,6 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3685,7 +3708,7 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
@@ -3695,7 +3718,7 @@
     <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="12.75">
+    <row r="1" spans="1:8" ht="13.5" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3721,12 +3744,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="12.75">
+    <row r="2" spans="1:8" ht="13.5" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3">
-        <v>59000000</v>
+      <c r="B2" s="101">
+        <v>58957347</v>
       </c>
       <c r="C2" s="4">
         <v>301340</v>
@@ -3738,7 +3761,7 @@
         <v>620000</v>
       </c>
       <c r="F2" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G2" s="3">
         <v>1800</v>
@@ -3747,12 +3770,12 @@
         <v>800</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="12.75">
+    <row r="3" spans="1:8" ht="13.5" thickBot="1">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3">
-        <v>17877000</v>
+      <c r="B3" s="102">
+        <v>17993485</v>
       </c>
       <c r="C3" s="4">
         <v>41543</v>
@@ -3764,7 +3787,7 @@
         <v>303000</v>
       </c>
       <c r="F3" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3">
         <v>300</v>
@@ -3773,12 +3796,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="12.75">
+    <row r="4" spans="1:8" ht="13.5" thickBot="1">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3">
-        <v>68000000</v>
+      <c r="B4" s="102">
+        <v>68775952</v>
       </c>
       <c r="C4" s="4">
         <v>551695</v>
@@ -3801,12 +3824,12 @@
         <v>484</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="12.75">
+    <row r="5" spans="1:8" ht="13.5" thickBot="1">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3">
-        <v>84524000</v>
+      <c r="B5" s="102">
+        <v>83516593</v>
       </c>
       <c r="C5" s="4">
         <v>357580</v>
@@ -3827,12 +3850,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="12.75">
+    <row r="6" spans="1:8" ht="13.5" thickBot="1">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3">
-        <v>10300000</v>
+      <c r="B6" s="101">
+        <v>10374050</v>
       </c>
       <c r="C6" s="3">
         <v>131957</v>
@@ -3853,12 +3876,12 @@
         <v>370</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="12.75">
+    <row r="7" spans="1:8" ht="13.5" thickBot="1">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3">
-        <v>8900000</v>
+      <c r="B7" s="101">
+        <v>9006644</v>
       </c>
       <c r="C7" s="4">
         <v>41285</v>
@@ -3879,12 +3902,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="12.75">
+    <row r="8" spans="1:8" ht="13.5" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3">
-        <v>47700000</v>
+      <c r="B8" s="101">
+        <v>48873996</v>
       </c>
       <c r="C8" s="3">
         <v>505990</v>
@@ -3905,12 +3928,12 @@
         <v>464</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="12.75">
+    <row r="9" spans="1:8" ht="13.5" thickBot="1">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="3">
-        <v>9100000</v>
+      <c r="B9" s="101">
+        <v>9177982</v>
       </c>
       <c r="C9" s="3">
         <v>83871</v>
@@ -3931,12 +3954,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="12.75">
+    <row r="10" spans="1:8" ht="13.5" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="3">
-        <v>5944000</v>
+      <c r="B10" s="101">
+        <v>5976992</v>
       </c>
       <c r="C10" s="4">
         <v>42933</v>
@@ -3957,23 +3980,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="12.75">
+    <row r="11" spans="1:8" ht="13.5" thickBot="1">
       <c r="A11" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="B11" s="3">
-        <v>1200000</v>
+        <v>19</v>
+      </c>
+      <c r="B11" s="102">
+        <v>5395980</v>
       </c>
       <c r="C11" s="3">
-        <v>9251</v>
+        <v>70273</v>
       </c>
       <c r="D11" s="3">
-        <v>35170</v>
+        <v>285400</v>
       </c>
       <c r="E11">
         <v>18000</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>1</v>
       </c>
       <c r="G11">
@@ -3983,23 +4006,23 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="12.75">
+    <row r="12" spans="1:8" ht="13.5" thickBot="1">
       <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="3">
-        <v>5300000</v>
+        <v>594</v>
+      </c>
+      <c r="B12" s="101">
+        <v>974666</v>
       </c>
       <c r="C12" s="3">
-        <v>70273</v>
+        <v>9251</v>
       </c>
       <c r="D12" s="3">
-        <v>285400</v>
+        <v>35170</v>
       </c>
       <c r="E12">
         <v>18000</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
@@ -4009,12 +4032,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="12.75">
+    <row r="13" spans="1:8" ht="13.5" thickBot="1">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="3">
-        <v>10300000</v>
+      <c r="B13" s="102">
+        <v>10694681</v>
       </c>
       <c r="C13" s="3">
         <v>92090</v>
@@ -4035,12 +4058,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="12.75">
+    <row r="14" spans="1:8" ht="13.5" thickBot="1">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3">
-        <v>37700000</v>
+      <c r="B14" s="101">
+        <v>36559233</v>
       </c>
       <c r="C14" s="3">
         <v>312685</v>
@@ -4061,12 +4084,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="12.75">
+    <row r="15" spans="1:8" ht="13.5" thickBot="1">
       <c r="A15" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B15" s="3">
-        <v>3900000</v>
+      <c r="B15" s="102">
+        <v>3868159</v>
       </c>
       <c r="C15" s="3">
         <v>56594</v>
@@ -4081,11 +4104,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="12.75">
+    <row r="16" spans="1:8" ht="13.5" thickBot="1">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="102">
         <v>1000000</v>
       </c>
       <c r="C16" s="4">
@@ -4107,12 +4130,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="12.75">
+    <row r="17" spans="1:8" ht="13.5" thickBot="1">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="3">
-        <v>11700000</v>
+      <c r="B17" s="101">
+        <v>11850296</v>
       </c>
       <c r="C17" s="4">
         <v>30528</v>
@@ -4133,12 +4156,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="12.75">
+    <row r="18" spans="1:8" ht="13.5" thickBot="1">
       <c r="A18" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B18" s="3">
-        <v>5500000</v>
+      <c r="B18" s="102">
+        <v>5572272</v>
       </c>
       <c r="C18" s="3">
         <v>323802</v>
@@ -4156,91 +4179,94 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="12.75">
+    <row r="19" spans="1:8" ht="13.5" thickBot="1">
       <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3">
-        <v>2800000</v>
+        <v>37</v>
+      </c>
+      <c r="B19" s="102">
+        <v>85518661</v>
       </c>
       <c r="C19" s="3">
-        <v>28748</v>
+        <v>783562</v>
       </c>
       <c r="D19" s="3">
-        <v>11710</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="12.75">
+        <v>756600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="13.5" thickBot="1">
       <c r="A20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="102">
+        <v>10905028</v>
+      </c>
+      <c r="C20" s="3">
+        <v>78867</v>
+      </c>
+      <c r="D20" s="3">
+        <v>151270</v>
+      </c>
+      <c r="F20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="13.5" thickBot="1">
+      <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3">
-        <v>6700000</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B21" s="101">
+        <v>6441421</v>
+      </c>
+      <c r="C21" s="3">
         <v>110994</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D21" s="3">
         <v>103390</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F21" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="12.75">
-      <c r="A21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="3">
-        <v>10900000</v>
-      </c>
-      <c r="C21" s="3">
-        <v>78867</v>
-      </c>
-      <c r="D21" s="3">
-        <v>151270</v>
-      </c>
-      <c r="F21" s="2">
+    <row r="22" spans="1:8" ht="13.5" thickBot="1">
+      <c r="A22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="102">
+        <v>2888278</v>
+      </c>
+      <c r="C22" s="3">
+        <v>65300</v>
+      </c>
+      <c r="D22" s="3">
+        <v>101610</v>
+      </c>
+      <c r="F22" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="12.75">
-      <c r="A22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="3">
-        <v>5400000</v>
-      </c>
-      <c r="C22" s="3">
-        <v>49035</v>
-      </c>
-      <c r="D22" s="3">
-        <v>43290</v>
-      </c>
-      <c r="F22" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="12.75">
+    <row r="23" spans="1:8" ht="13.5" thickBot="1">
       <c r="A23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="3">
-        <v>1300000</v>
+        <v>25</v>
+      </c>
+      <c r="B23" s="101">
+        <v>19055364</v>
       </c>
       <c r="C23" s="3">
-        <v>45339</v>
+        <v>238391</v>
       </c>
       <c r="D23" s="3">
-        <v>46180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="12.75">
+        <v>97360</v>
+      </c>
+      <c r="F23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="13.5" thickBot="1">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3">
-        <v>9600000</v>
+      <c r="B24" s="102">
+        <v>9562065</v>
       </c>
       <c r="C24" s="3">
         <v>93030</v>
@@ -4249,126 +4275,123 @@
         <v>94080</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="12.75">
+    <row r="25" spans="1:8" ht="13.5" thickBot="1">
       <c r="A25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="3">
-        <v>1800000</v>
+        <v>27</v>
+      </c>
+      <c r="B25" s="102">
+        <v>10569709</v>
       </c>
       <c r="C25" s="3">
-        <v>64589</v>
+        <v>450295</v>
       </c>
       <c r="D25" s="3">
-        <v>51910</v>
+        <v>83480</v>
       </c>
       <c r="F25" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="12.75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="13.5" thickBot="1">
       <c r="A26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="3">
-        <v>2800000</v>
+        <v>29</v>
+      </c>
+      <c r="B26" s="102">
+        <v>6586476</v>
       </c>
       <c r="C26" s="3">
-        <v>65300</v>
+        <v>77474</v>
       </c>
       <c r="D26" s="3">
-        <v>101610</v>
+        <v>53370</v>
       </c>
       <c r="F26" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="12.75">
+    <row r="27" spans="1:8" ht="13.5" thickBot="1">
       <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3">
-        <v>19000000</v>
+        <v>30</v>
+      </c>
+      <c r="B27" s="102">
+        <v>1869570</v>
       </c>
       <c r="C27" s="3">
-        <v>238391</v>
+        <v>64589</v>
       </c>
       <c r="D27" s="3">
-        <v>97360</v>
+        <v>51910</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="12.75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="13.5" thickBot="1">
       <c r="A28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="3">
-        <v>6700000</v>
+        <v>31</v>
+      </c>
+      <c r="B28" s="102">
+        <v>1372341</v>
       </c>
       <c r="C28" s="3">
-        <v>77474</v>
+        <v>45339</v>
       </c>
       <c r="D28" s="3">
-        <v>53370</v>
-      </c>
-      <c r="F28" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="12.75">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="13.5" thickBot="1">
       <c r="A29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="101">
+        <v>5422069</v>
+      </c>
+      <c r="C29" s="3">
+        <v>49035</v>
+      </c>
+      <c r="D29" s="3">
+        <v>43290</v>
+      </c>
+      <c r="F29" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="13.5" thickBot="1">
+      <c r="A30" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B29" s="3">
-        <v>2100000</v>
-      </c>
-      <c r="C29" s="3">
+      <c r="B30" s="102">
+        <v>2127400</v>
+      </c>
+      <c r="C30" s="3">
         <v>20273</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D30" s="3">
         <v>15560</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F30" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="12.75">
-      <c r="A30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="3">
-        <v>10600000</v>
-      </c>
-      <c r="C30" s="3">
-        <v>450295</v>
-      </c>
-      <c r="D30" s="3">
-        <v>83480</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="12.75">
+    <row r="31" spans="1:8" ht="13.5" thickBot="1">
       <c r="A31" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3">
-        <v>86500000</v>
+        <v>36</v>
+      </c>
+      <c r="B31" s="101">
+        <v>2377128</v>
       </c>
       <c r="C31" s="3">
-        <v>783562</v>
+        <v>28748</v>
       </c>
       <c r="D31" s="3">
-        <v>756600</v>
+        <v>11710</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H31" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H31">
-      <sortCondition descending="1" ref="E1:E31"/>
+      <sortCondition descending="1" ref="E2:E31"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H31">
@@ -14741,7 +14764,7 @@
       <c r="A2" s="37" t="s">
         <v>365</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="95" t="s">
         <v>366</v>
       </c>
       <c r="C2" s="94"/>
@@ -14768,7 +14791,7 @@
       <c r="A3" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="B3" s="98">
+      <c r="B3" s="96">
         <v>45586.958333333336</v>
       </c>
       <c r="C3" s="94"/>
@@ -14844,7 +14867,7 @@
       <c r="U5" s="17"/>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="95" t="s">
         <v>371</v>
       </c>
       <c r="B6" s="94"/>
@@ -14924,46 +14947,46 @@
       <c r="A9" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="B9" s="95">
+      <c r="B9" s="97">
         <v>2011</v>
       </c>
-      <c r="C9" s="96"/>
-      <c r="D9" s="95">
+      <c r="C9" s="98"/>
+      <c r="D9" s="97">
         <v>2012</v>
       </c>
-      <c r="E9" s="96"/>
-      <c r="F9" s="95">
+      <c r="E9" s="98"/>
+      <c r="F9" s="97">
         <v>2013</v>
       </c>
-      <c r="G9" s="96"/>
-      <c r="H9" s="95">
+      <c r="G9" s="98"/>
+      <c r="H9" s="97">
         <v>2014</v>
       </c>
-      <c r="I9" s="96"/>
-      <c r="J9" s="95">
+      <c r="I9" s="98"/>
+      <c r="J9" s="97">
         <v>2015</v>
       </c>
-      <c r="K9" s="96"/>
-      <c r="L9" s="95">
+      <c r="K9" s="98"/>
+      <c r="L9" s="97">
         <v>2016</v>
       </c>
-      <c r="M9" s="96"/>
-      <c r="N9" s="95">
+      <c r="M9" s="98"/>
+      <c r="N9" s="97">
         <v>2017</v>
       </c>
-      <c r="O9" s="96"/>
-      <c r="P9" s="95">
+      <c r="O9" s="98"/>
+      <c r="P9" s="97">
         <v>2018</v>
       </c>
-      <c r="Q9" s="96"/>
-      <c r="R9" s="95">
+      <c r="Q9" s="98"/>
+      <c r="R9" s="97">
         <v>2019</v>
       </c>
-      <c r="S9" s="96"/>
-      <c r="T9" s="95">
+      <c r="S9" s="98"/>
+      <c r="T9" s="97">
         <v>2020</v>
       </c>
-      <c r="U9" s="96"/>
+      <c r="U9" s="98"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="41" t="s">
@@ -16831,12 +16854,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="P9:Q9"/>
     <mergeCell ref="R9:S9"/>
@@ -16848,6 +16865,12 @@
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="N9:O9"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>

--- a/posts/2026-04-26_asturias-mancha-quesera/AOC-Mancha_quesera_europa_update-claude-202604.xlsx
+++ b/posts/2026-04-26_asturias-mancha-quesera/AOC-Mancha_quesera_europa_update-claude-202604.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanr\GitHub\blog\posts\2026-04-26_asturias-mancha-quesera\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/blog-trabajo/2026-04-26_asturias-mancha-quesera/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1FD8A8-9953-4FFB-BAAD-C0E12AA059BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{A835B32E-AF8A-43C3-A7DE-085E6D9B2406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDBB561E-CF0B-46CF-9B83-F69E5260759E}"/>
   <bookViews>
-    <workbookView xWindow="5190" yWindow="3135" windowWidth="17820" windowHeight="11190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prod por pais" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="Dinamarca" sheetId="15" r:id="rId15"/>
     <sheet name="Países Bajos" sheetId="16" r:id="rId16"/>
     <sheet name="Grecia" sheetId="17" r:id="rId17"/>
+    <sheet name="Gemini-quesos no DOP" sheetId="18" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prod por pais'!$A$1:$H$31</definedName>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="624">
   <si>
     <t>pais</t>
   </si>
@@ -2381,6 +2382,139 @@
   <si>
     <t>Chipre</t>
   </si>
+  <si>
+    <t>Variedades Totales (Aprox.)</t>
+  </si>
+  <si>
+    <t>Variedades DOP/IGP</t>
+  </si>
+  <si>
+    <t>Relación de Diversidad</t>
+  </si>
+  <si>
+    <t>1,200 - 1,600</t>
+  </si>
+  <si>
+    <t>Es el país con más micro-variedades de granja.</t>
+  </si>
+  <si>
+    <t>600 - 800</t>
+  </si>
+  <si>
+    <t>Gran enfoque en variantes de pastas hiladas y pecorinos.</t>
+  </si>
+  <si>
+    <t>Altísima densidad: 1 variedad por cada 90 km².</t>
+  </si>
+  <si>
+    <t>150 - 200</t>
+  </si>
+  <si>
+    <t>Destaca la riqueza de quesos de cabra y mezclas.</t>
+  </si>
+  <si>
+    <t>40 - 50</t>
+  </si>
+  <si>
+    <t>Concentración masiva (casi el 25% del total español).</t>
+  </si>
+  <si>
+    <t>300 - 400</t>
+  </si>
+  <si>
+    <t>Mucha producción artesanal en Baviera y el Norte.</t>
+  </si>
+  <si>
+    <t>700 - 1,000</t>
+  </si>
+  <si>
+    <t>Explosión de "Modern British Cheese" artesanal.</t>
+  </si>
+  <si>
+    <t>Muchas variaciones de Gouda con semillas/especias.</t>
+  </si>
+  <si>
+    <t>70 - 100</t>
+  </si>
+  <si>
+    <t>Fuerte peso de la producción doméstica no comercial.</t>
+  </si>
+  <si>
+    <t>120 - 150</t>
+  </si>
+  <si>
+    <r>
+      <t>Especializados en quesos de heno (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Heumilch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>200 - 300</t>
+  </si>
+  <si>
+    <t>2 (EU)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inmensa variedad de quesos </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tulum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (en piel de cabra).</t>
+    </r>
+  </si>
+  <si>
+    <t>Gran tradición de quesos de abadía.</t>
+  </si>
+  <si>
+    <t>50 - 80</t>
+  </si>
+  <si>
+    <t>Crecimiento rápido de quesos azules de autor.</t>
+  </si>
+  <si>
+    <t>50 - 60</t>
+  </si>
+  <si>
+    <t>400 - 500</t>
+  </si>
 </sst>
 </file>
 
@@ -2389,7 +2523,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy\ h:mm"/>
   </numFmts>
-  <fonts count="50">
+  <fonts count="53">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2696,8 +2830,31 @@
       <color rgb="FF000000"/>
       <name val="Inherit"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2791,12 +2948,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE1E1E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8F8F8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2988,16 +3139,16 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFDFE2E5"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color rgb="FFDFE2E5"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color rgb="FFDFE2E5"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFDFE2E5"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3005,7 +3156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3239,6 +3390,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3256,12 +3419,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3458,6 +3615,10 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3705,10 +3866,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
@@ -3718,7 +3879,7 @@
     <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.5" thickBot="1">
+    <row r="1" spans="1:10" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3744,12 +3905,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.5" thickBot="1">
+    <row r="2" spans="1:10" ht="12.75">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="101">
-        <v>58957347</v>
+      <c r="B2" s="3">
+        <v>59000000</v>
       </c>
       <c r="C2" s="4">
         <v>301340</v>
@@ -3761,7 +3922,7 @@
         <v>620000</v>
       </c>
       <c r="F2" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G2" s="3">
         <v>1800</v>
@@ -3769,13 +3930,17 @@
       <c r="H2" s="5">
         <v>800</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="13.5" thickBot="1">
+      <c r="J2">
+        <f>G2/C2*100</f>
+        <v>0.597331917435455</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="12.75">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="102">
-        <v>17993485</v>
+      <c r="B3" s="3">
+        <v>17877000</v>
       </c>
       <c r="C3" s="4">
         <v>41543</v>
@@ -3787,7 +3952,7 @@
         <v>303000</v>
       </c>
       <c r="F3" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3">
         <v>300</v>
@@ -3796,12 +3961,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.5" thickBot="1">
+    <row r="4" spans="1:10" ht="12.75">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="102">
-        <v>68775952</v>
+      <c r="B4" s="3">
+        <v>68000000</v>
       </c>
       <c r="C4" s="4">
         <v>551695</v>
@@ -3824,12 +3989,12 @@
         <v>484</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.5" thickBot="1">
+    <row r="5" spans="1:10" ht="12.75">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="102">
-        <v>83516593</v>
+      <c r="B5" s="3">
+        <v>84524000</v>
       </c>
       <c r="C5" s="4">
         <v>357580</v>
@@ -3850,12 +4015,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="13.5" thickBot="1">
+    <row r="6" spans="1:10" ht="12.75">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="101">
-        <v>10374050</v>
+      <c r="B6" s="3">
+        <v>10300000</v>
       </c>
       <c r="C6" s="3">
         <v>131957</v>
@@ -3876,12 +4041,12 @@
         <v>370</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.5" thickBot="1">
+    <row r="7" spans="1:10" ht="12.75">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="101">
-        <v>9006644</v>
+      <c r="B7" s="3">
+        <v>8900000</v>
       </c>
       <c r="C7" s="4">
         <v>41285</v>
@@ -3902,12 +4067,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.5" thickBot="1">
+    <row r="8" spans="1:10" ht="12.75">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="101">
-        <v>48873996</v>
+      <c r="B8" s="3">
+        <v>47700000</v>
       </c>
       <c r="C8" s="3">
         <v>505990</v>
@@ -3928,12 +4093,12 @@
         <v>464</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="13.5" thickBot="1">
+    <row r="9" spans="1:10" ht="12.75">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="101">
-        <v>9177982</v>
+      <c r="B9" s="3">
+        <v>9100000</v>
       </c>
       <c r="C9" s="3">
         <v>83871</v>
@@ -3954,12 +4119,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13.5" thickBot="1">
+    <row r="10" spans="1:10" ht="12.75">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="101">
-        <v>5976992</v>
+      <c r="B10" s="3">
+        <v>5944000</v>
       </c>
       <c r="C10" s="4">
         <v>42933</v>
@@ -3980,23 +4145,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.5" thickBot="1">
+    <row r="11" spans="1:10" ht="12.75">
       <c r="A11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="102">
-        <v>5395980</v>
+        <v>594</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1200000</v>
       </c>
       <c r="C11" s="3">
-        <v>70273</v>
+        <v>9251</v>
       </c>
       <c r="D11" s="3">
-        <v>285400</v>
+        <v>35170</v>
       </c>
       <c r="E11">
         <v>18000</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
@@ -4006,23 +4171,23 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.5" thickBot="1">
+    <row r="12" spans="1:10" ht="12.75">
       <c r="A12" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="B12" s="101">
-        <v>974666</v>
+        <v>19</v>
+      </c>
+      <c r="B12" s="3">
+        <v>5300000</v>
       </c>
       <c r="C12" s="3">
-        <v>9251</v>
+        <v>70273</v>
       </c>
       <c r="D12" s="3">
-        <v>35170</v>
+        <v>285400</v>
       </c>
       <c r="E12">
         <v>18000</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>1</v>
       </c>
       <c r="G12">
@@ -4032,12 +4197,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.5" thickBot="1">
+    <row r="13" spans="1:10" ht="12.75">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="102">
-        <v>10694681</v>
+      <c r="B13" s="3">
+        <v>10300000</v>
       </c>
       <c r="C13" s="3">
         <v>92090</v>
@@ -4058,12 +4223,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.5" thickBot="1">
+    <row r="14" spans="1:10" ht="12.75">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="101">
-        <v>36559233</v>
+      <c r="B14" s="3">
+        <v>37700000</v>
       </c>
       <c r="C14" s="3">
         <v>312685</v>
@@ -4084,12 +4249,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.5" thickBot="1">
+    <row r="15" spans="1:10" ht="12.75">
       <c r="A15" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B15" s="102">
-        <v>3868159</v>
+      <c r="B15" s="3">
+        <v>3900000</v>
       </c>
       <c r="C15" s="3">
         <v>56594</v>
@@ -4104,18 +4269,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.5" thickBot="1">
+    <row r="16" spans="1:10" ht="12.75">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="102">
+      <c r="B16" s="3">
         <v>1000000</v>
       </c>
       <c r="C16" s="4">
         <v>10604</v>
       </c>
       <c r="D16" s="3">
-        <v>25168</v>
+        <v>35310</v>
       </c>
       <c r="E16" s="2">
         <v>660</v>
@@ -4130,12 +4295,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13.5" thickBot="1">
+    <row r="17" spans="1:8" ht="12.75">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="101">
-        <v>11850296</v>
+      <c r="B17" s="3">
+        <v>11700000</v>
       </c>
       <c r="C17" s="4">
         <v>30528</v>
@@ -4156,12 +4321,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.5" thickBot="1">
+    <row r="18" spans="1:8" ht="12.75">
       <c r="A18" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B18" s="102">
-        <v>5572272</v>
+      <c r="B18" s="3">
+        <v>5500000</v>
       </c>
       <c r="C18" s="3">
         <v>323802</v>
@@ -4179,94 +4344,91 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="13.5" thickBot="1">
+    <row r="19" spans="1:8" ht="12.75">
       <c r="A19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="102">
-        <v>85518661</v>
+        <v>36</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2800000</v>
       </c>
       <c r="C19" s="3">
-        <v>783562</v>
+        <v>28748</v>
       </c>
       <c r="D19" s="3">
-        <v>756600</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="13.5" thickBot="1">
+        <v>11710</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="12.75">
       <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="3">
+        <v>6700000</v>
+      </c>
+      <c r="C20" s="3">
+        <v>110994</v>
+      </c>
+      <c r="D20" s="3">
+        <v>103390</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="12.75">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="102">
-        <v>10905028</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B21" s="3">
+        <v>10900000</v>
+      </c>
+      <c r="C21" s="3">
         <v>78867</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D21" s="3">
         <v>151270</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F21" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.5" thickBot="1">
-      <c r="A21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="101">
-        <v>6441421</v>
-      </c>
-      <c r="C21" s="3">
-        <v>110994</v>
-      </c>
-      <c r="D21" s="3">
-        <v>103390</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="13.5" thickBot="1">
+    <row r="22" spans="1:8" ht="12.75">
       <c r="A22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="102">
-        <v>2888278</v>
+        <v>32</v>
+      </c>
+      <c r="B22" s="3">
+        <v>5400000</v>
       </c>
       <c r="C22" s="3">
-        <v>65300</v>
+        <v>49035</v>
       </c>
       <c r="D22" s="3">
-        <v>101610</v>
+        <v>43290</v>
       </c>
       <c r="F22" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="13.5" thickBot="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="12.75">
       <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="101">
-        <v>19055364</v>
+        <v>31</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1300000</v>
       </c>
       <c r="C23" s="3">
-        <v>238391</v>
+        <v>45339</v>
       </c>
       <c r="D23" s="3">
-        <v>97360</v>
-      </c>
-      <c r="F23" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="13.5" thickBot="1">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="12.75">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="102">
-        <v>9562065</v>
+      <c r="B24" s="3">
+        <v>9600000</v>
       </c>
       <c r="C24" s="3">
         <v>93030</v>
@@ -4275,123 +4437,126 @@
         <v>94080</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.5" thickBot="1">
+    <row r="25" spans="1:8" ht="12.75">
       <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="102">
-        <v>10569709</v>
+        <v>30</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1800000</v>
       </c>
       <c r="C25" s="3">
-        <v>450295</v>
+        <v>64589</v>
       </c>
       <c r="D25" s="3">
-        <v>83480</v>
+        <v>51910</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="13.5" thickBot="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="12.75">
       <c r="A26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="102">
-        <v>6586476</v>
+        <v>23</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2800000</v>
       </c>
       <c r="C26" s="3">
-        <v>77474</v>
+        <v>65300</v>
       </c>
       <c r="D26" s="3">
-        <v>53370</v>
+        <v>101610</v>
       </c>
       <c r="F26" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="13.5" thickBot="1">
+    <row r="27" spans="1:8" ht="12.75">
       <c r="A27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="102">
-        <v>1869570</v>
+        <v>25</v>
+      </c>
+      <c r="B27" s="3">
+        <v>19000000</v>
       </c>
       <c r="C27" s="3">
-        <v>64589</v>
+        <v>238391</v>
       </c>
       <c r="D27" s="3">
-        <v>51910</v>
+        <v>97360</v>
       </c>
       <c r="F27" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="12.75">
+      <c r="A28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="3">
+        <v>6700000</v>
+      </c>
+      <c r="C28" s="3">
+        <v>77474</v>
+      </c>
+      <c r="D28" s="3">
+        <v>53370</v>
+      </c>
+      <c r="F28" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.5" thickBot="1">
-      <c r="A28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="102">
-        <v>1372341</v>
-      </c>
-      <c r="C28" s="3">
-        <v>45339</v>
-      </c>
-      <c r="D28" s="3">
-        <v>46180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="13.5" thickBot="1">
+    <row r="29" spans="1:8" ht="12.75">
       <c r="A29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="101">
-        <v>5422069</v>
+        <v>290</v>
+      </c>
+      <c r="B29" s="3">
+        <v>2100000</v>
       </c>
       <c r="C29" s="3">
-        <v>49035</v>
+        <v>20273</v>
       </c>
       <c r="D29" s="3">
-        <v>43290</v>
+        <v>15560</v>
       </c>
       <c r="F29" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="13.5" thickBot="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="12.75">
       <c r="A30" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B30" s="102">
-        <v>2127400</v>
+        <v>27</v>
+      </c>
+      <c r="B30" s="3">
+        <v>10600000</v>
       </c>
       <c r="C30" s="3">
-        <v>20273</v>
+        <v>450295</v>
       </c>
       <c r="D30" s="3">
-        <v>15560</v>
+        <v>83480</v>
       </c>
       <c r="F30" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="13.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="12.75">
       <c r="A31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="101">
-        <v>2377128</v>
+        <v>37</v>
+      </c>
+      <c r="B31" s="3">
+        <v>86500000</v>
       </c>
       <c r="C31" s="3">
-        <v>28748</v>
+        <v>783562</v>
       </c>
       <c r="D31" s="3">
-        <v>11710</v>
+        <v>756600</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H31" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H31">
-      <sortCondition descending="1" ref="E2:E31"/>
+      <sortCondition descending="1" ref="E1:E31"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H31">
@@ -4678,16 +4843,16 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="103" t="s">
         <v>422</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="17"/>
@@ -4716,10 +4881,10 @@
       <c r="B4" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="C4" s="99" t="s">
+      <c r="C4" s="103" t="s">
         <v>424</v>
       </c>
-      <c r="D4" s="94"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
@@ -5024,23 +5189,23 @@
       <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="103" t="s">
         <v>425</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="99" t="s">
+      <c r="A25" s="103" t="s">
         <v>426</v>
       </c>
-      <c r="B25" s="94"/>
-      <c r="C25" s="94"/>
+      <c r="B25" s="98"/>
+      <c r="C25" s="98"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
@@ -5048,11 +5213,11 @@
       <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="99" t="s">
+      <c r="A26" s="103" t="s">
         <v>427</v>
       </c>
-      <c r="B26" s="94"/>
-      <c r="C26" s="94"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="98"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
@@ -5060,10 +5225,10 @@
       <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="99" t="s">
+      <c r="A27" s="103" t="s">
         <v>428</v>
       </c>
-      <c r="B27" s="94"/>
+      <c r="B27" s="98"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
@@ -6169,10 +6334,10 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A38" s="100" t="s">
+      <c r="A38" s="104" t="s">
         <v>469</v>
       </c>
-      <c r="B38" s="94"/>
+      <c r="B38" s="98"/>
       <c r="C38" s="68">
         <v>471181</v>
       </c>
@@ -6256,10 +6421,10 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
-      <c r="A42" s="100" t="s">
+      <c r="A42" s="104" t="s">
         <v>469</v>
       </c>
-      <c r="B42" s="94"/>
+      <c r="B42" s="98"/>
       <c r="C42" s="68">
         <v>50176</v>
       </c>
@@ -6514,10 +6679,10 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
-      <c r="A52" s="100" t="s">
+      <c r="A52" s="104" t="s">
         <v>469</v>
       </c>
-      <c r="B52" s="94"/>
+      <c r="B52" s="98"/>
       <c r="C52" s="68">
         <v>33212</v>
       </c>
@@ -6600,10 +6765,10 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
-      <c r="A56" s="100" t="s">
+      <c r="A56" s="104" t="s">
         <v>469</v>
       </c>
-      <c r="B56" s="94"/>
+      <c r="B56" s="98"/>
       <c r="C56" s="71">
         <v>10</v>
       </c>
@@ -8633,6 +8798,218 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{381058A3-399E-444A-AF76-C221E27CA0A5}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="52.42578125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A1" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="93" t="s">
+        <v>595</v>
+      </c>
+      <c r="C1" s="93" t="s">
+        <v>596</v>
+      </c>
+      <c r="D1" s="94" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A2" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="95" t="s">
+        <v>598</v>
+      </c>
+      <c r="C2" s="95">
+        <v>54</v>
+      </c>
+      <c r="D2" s="96" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A3" s="95" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="95" t="s">
+        <v>600</v>
+      </c>
+      <c r="C3" s="95">
+        <v>56</v>
+      </c>
+      <c r="D3" s="96" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A4" s="95" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="95" t="s">
+        <v>623</v>
+      </c>
+      <c r="C4" s="95">
+        <v>12</v>
+      </c>
+      <c r="D4" s="96" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A5" s="95" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="95" t="s">
+        <v>603</v>
+      </c>
+      <c r="C5" s="95">
+        <v>32</v>
+      </c>
+      <c r="D5" s="96" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A6" s="95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="95" t="s">
+        <v>605</v>
+      </c>
+      <c r="C6" s="95">
+        <v>5</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A7" s="95" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>607</v>
+      </c>
+      <c r="C7" s="95">
+        <v>13</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A8" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="95" t="s">
+        <v>609</v>
+      </c>
+      <c r="C8" s="95">
+        <v>15</v>
+      </c>
+      <c r="D8" s="96" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A9" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="95" t="s">
+        <v>605</v>
+      </c>
+      <c r="C9" s="95">
+        <v>8</v>
+      </c>
+      <c r="D9" s="96" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A10" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="95" t="s">
+        <v>612</v>
+      </c>
+      <c r="C10" s="95">
+        <v>21</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A11" s="95" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="95" t="s">
+        <v>614</v>
+      </c>
+      <c r="C11" s="95">
+        <v>6</v>
+      </c>
+      <c r="D11" s="96" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A12" s="95" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="95" t="s">
+        <v>616</v>
+      </c>
+      <c r="C12" s="95" t="s">
+        <v>617</v>
+      </c>
+      <c r="D12" s="96" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A13" s="95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>622</v>
+      </c>
+      <c r="C13" s="95">
+        <v>2</v>
+      </c>
+      <c r="D13" s="96" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="13.5" thickBot="1">
+      <c r="A14" s="95" t="s">
+        <v>592</v>
+      </c>
+      <c r="B14" s="95" t="s">
+        <v>620</v>
+      </c>
+      <c r="C14" s="95">
+        <v>3</v>
+      </c>
+      <c r="D14" s="96" t="s">
+        <v>621</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
@@ -14736,11 +15113,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="97" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
@@ -14764,19 +15141,19 @@
       <c r="A2" s="37" t="s">
         <v>365</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="99" t="s">
         <v>366</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
       <c r="M2" s="17"/>
       <c r="N2" s="17"/>
       <c r="O2" s="17"/>
@@ -14791,10 +15168,10 @@
       <c r="A3" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="B3" s="96">
+      <c r="B3" s="100">
         <v>45586.958333333336</v>
       </c>
-      <c r="C3" s="94"/>
+      <c r="C3" s="98"/>
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
       <c r="F3" s="17"/>
@@ -14844,10 +15221,10 @@
         <v>369</v>
       </c>
       <c r="B5" s="17"/>
-      <c r="C5" s="93" t="s">
+      <c r="C5" s="97" t="s">
         <v>370</v>
       </c>
-      <c r="D5" s="94"/>
+      <c r="D5" s="98"/>
       <c r="E5" s="17"/>
       <c r="F5" s="17"/>
       <c r="G5" s="17"/>
@@ -14867,14 +15244,14 @@
       <c r="U5" s="17"/>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="95" t="s">
+      <c r="A6" s="99" t="s">
         <v>371</v>
       </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="93" t="s">
+      <c r="B6" s="98"/>
+      <c r="C6" s="97" t="s">
         <v>372</v>
       </c>
-      <c r="D6" s="94"/>
+      <c r="D6" s="98"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
@@ -14898,12 +15275,12 @@
         <v>373</v>
       </c>
       <c r="B7" s="17"/>
-      <c r="C7" s="93" t="s">
+      <c r="C7" s="97" t="s">
         <v>374</v>
       </c>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
@@ -14947,46 +15324,46 @@
       <c r="A9" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="B9" s="97">
+      <c r="B9" s="101">
         <v>2011</v>
       </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="97">
+      <c r="C9" s="102"/>
+      <c r="D9" s="101">
         <v>2012</v>
       </c>
-      <c r="E9" s="98"/>
-      <c r="F9" s="97">
+      <c r="E9" s="102"/>
+      <c r="F9" s="101">
         <v>2013</v>
       </c>
-      <c r="G9" s="98"/>
-      <c r="H9" s="97">
+      <c r="G9" s="102"/>
+      <c r="H9" s="101">
         <v>2014</v>
       </c>
-      <c r="I9" s="98"/>
-      <c r="J9" s="97">
+      <c r="I9" s="102"/>
+      <c r="J9" s="101">
         <v>2015</v>
       </c>
-      <c r="K9" s="98"/>
-      <c r="L9" s="97">
+      <c r="K9" s="102"/>
+      <c r="L9" s="101">
         <v>2016</v>
       </c>
-      <c r="M9" s="98"/>
-      <c r="N9" s="97">
+      <c r="M9" s="102"/>
+      <c r="N9" s="101">
         <v>2017</v>
       </c>
-      <c r="O9" s="98"/>
-      <c r="P9" s="97">
+      <c r="O9" s="102"/>
+      <c r="P9" s="101">
         <v>2018</v>
       </c>
-      <c r="Q9" s="98"/>
-      <c r="R9" s="97">
+      <c r="Q9" s="102"/>
+      <c r="R9" s="101">
         <v>2019</v>
       </c>
-      <c r="S9" s="98"/>
-      <c r="T9" s="97">
+      <c r="S9" s="102"/>
+      <c r="T9" s="101">
         <v>2020</v>
       </c>
-      <c r="U9" s="98"/>
+      <c r="U9" s="102"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="41" t="s">

--- a/posts/2026-04-26_asturias-mancha-quesera/AOC-Mancha_quesera_europa_update-claude-202604.xlsx
+++ b/posts/2026-04-26_asturias-mancha-quesera/AOC-Mancha_quesera_europa_update-claude-202604.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/blog-trabajo/2026-04-26_asturias-mancha-quesera/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{A835B32E-AF8A-43C3-A7DE-085E6D9B2406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDBB561E-CF0B-46CF-9B83-F69E5260759E}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{A835B32E-AF8A-43C3-A7DE-085E6D9B2406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFE72069-673A-49A0-BAB6-A7F1CE972576}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="624">
   <si>
     <t>pais</t>
   </si>
@@ -4185,16 +4185,16 @@
         <v>285400</v>
       </c>
       <c r="E12">
-        <v>18000</v>
+        <v>4000</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="12.75">
@@ -10638,9 +10638,15 @@
       <c r="A86" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B86" s="10"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="10"/>
+      <c r="B86" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86" s="11">
+        <v>4000</v>
+      </c>
+      <c r="D86" s="10">
+        <v>2023</v>
+      </c>
       <c r="E86" s="10" t="s">
         <v>19</v>
       </c>
